--- a/Content/en_estimate_A.xlsx
+++ b/Content/en_estimate_A.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F43C748-BEC5-4127-855C-D67B33ED2951}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B37B11-049C-4549-B4A9-1AC4388DBA47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">                 INCHEON, KOREA</t>
   </si>
@@ -92,22 +92,9 @@
     <t>BANK INFORMATION</t>
   </si>
   <si>
-    <t>BANK NAME : WOORI BANK JUAN INDUSTRIAL BRANCH</t>
-  </si>
-  <si>
-    <t>BANK ADDRESS : 539-1 GAJWA-DONG SEO-GU,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      INCHEON KOREA JUAN INDUSTRIAL BRANCH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SWIFT CODE : HVBKKRSEXXX</t>
   </si>
   <si>
-    <t>ACCOUNT NO. : 1081-700-147963</t>
-  </si>
-  <si>
     <t>Looking forward to your valued order for the above offer,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -117,6 +104,46 @@
   </si>
   <si>
     <t xml:space="preserve">Messrs. : </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       MR. JOONG HYUN KI / PRESIDENT</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUSTOMER_NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK NAME : WOORI BANK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK ADDRESS : 104-8 2F DOHWA-DONG NAM-GU, INCHEON KOREA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRANCH NAME : JUAN INDUSTRIAL COMPLEX BRANCH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCOUNT NO. : 1081-700-147963(USD/JPY/EUR/CNY) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1005-803-477176(KRW)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -131,7 +158,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +327,21 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -421,7 +463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -521,41 +563,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -944,30 +989,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -981,15 +1026,15 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -998,8 +1043,8 @@
       <c r="D8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
@@ -1010,14 +1055,14 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -1080,21 +1125,21 @@
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="19"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
+      <c r="B18" s="34"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21"/>
@@ -1118,7 +1163,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="28"/>
@@ -1128,7 +1173,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="29"/>
@@ -1138,7 +1183,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B23" s="25"/>
       <c r="D23" s="27"/>
@@ -1147,7 +1192,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B24" s="30"/>
       <c r="D24" s="27"/>
@@ -1156,7 +1201,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B25" s="31"/>
       <c r="D25" s="27"/>
@@ -1164,7 +1209,9 @@
       <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
+      <c r="A26" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
       <c r="D26" s="27"/>
@@ -1172,24 +1219,24 @@
       <c r="F26" s="24"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
+      <c r="A27" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
+      <c r="A28" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="32"/>
@@ -1200,18 +1247,17 @@
       <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
+      <c r="A32" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="35" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A10:F10"/>
@@ -1220,6 +1266,12 @@
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Content/en_estimate_A.xlsx
+++ b/Content/en_estimate_A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B37B11-049C-4549-B4A9-1AC4388DBA47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD30262-D572-4D13-AA02-C31388726BD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
   </bookViews>
@@ -77,14 +77,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>Unit price</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amount</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -145,6 +137,12 @@
       <t>1005-803-477176(KRW)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>Amount</t>
   </si>
 </sst>
 </file>
@@ -463,7 +461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -572,6 +570,27 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -581,25 +600,13 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -989,30 +996,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -1026,15 +1033,15 @@
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -1043,8 +1050,8 @@
       <c r="D8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
     </row>
     <row r="9" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
@@ -1055,14 +1062,14 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
     </row>
     <row r="11" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -1101,10 +1108,10 @@
         <v>11</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,40 +1119,40 @@
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="33"/>
       <c r="C17" s="19"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="34"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
@@ -1153,7 +1160,7 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="26"/>
@@ -1163,7 +1170,7 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="28"/>
@@ -1173,7 +1180,7 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="29"/>
@@ -1183,7 +1190,7 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="25"/>
       <c r="D23" s="27"/>
@@ -1192,7 +1199,7 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B24" s="30"/>
       <c r="D24" s="27"/>
@@ -1201,7 +1208,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="31"/>
       <c r="D25" s="27"/>
@@ -1210,7 +1217,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -1219,24 +1226,24 @@
       <c r="F26" s="24"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
+      <c r="A27" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
+      <c r="A28" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="32"/>
@@ -1247,17 +1254,23 @@
       <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
+      <c r="A32" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
       <c r="D32" s="35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A10:F10"/>
@@ -1266,12 +1279,6 @@
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Content/en_estimate_A.xlsx
+++ b/Content/en_estimate_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\yonwoo\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD30262-D572-4D13-AA02-C31388726BD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A4F50A-7019-4640-B85F-C367FD9E25F8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -149,12 +149,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$-409]d&quot;-&quot;mmm&quot;-&quot;yy;@"/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
     <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -570,6 +571,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -591,22 +601,13 @@
     <xf numFmtId="178" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -996,30 +997,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -1040,8 +1041,8 @@
       <c r="D7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -1050,8 +1051,8 @@
       <c r="D8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
@@ -1062,14 +1063,14 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -1132,19 +1133,19 @@
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:8" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="33"/>
       <c r="C17" s="19"/>
-      <c r="D17" s="41"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="47"/>
       <c r="F17" s="47"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="34"/>
       <c r="C18" s="20"/>
-      <c r="D18" s="42"/>
+      <c r="D18" s="45"/>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
     </row>
@@ -1226,24 +1227,24 @@
       <c r="F26" s="24"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="32"/>
@@ -1254,23 +1255,17 @@
       <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="35" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="E7:F7"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A10:F10"/>
@@ -1279,10 +1274,16 @@
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>